--- a/filer/24246930_dlg.xlsx
+++ b/filer/24246930_dlg.xlsx
@@ -5413,10 +5413,10 @@
         <v>198000</v>
       </c>
       <c r="E36" s="16" t="n">
-        <v>195000</v>
+        <v>5070000</v>
       </c>
       <c r="F36" s="16" t="n">
-        <v>196000</v>
+        <v>4821000</v>
       </c>
     </row>
     <row r="37">
@@ -5585,10 +5585,10 @@
         <v>1883000</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>1775000</v>
+        <v>5397000</v>
       </c>
       <c r="F47" s="16" t="n">
-        <v>1829000</v>
+        <v>5280000</v>
       </c>
     </row>
     <row r="48">
@@ -6879,7 +6879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7056,29 +7056,25 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentDerivativeFinancialAssets</t>
+          <t>ifrs-full:CurrentFinancialLiabilities</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentDerivativeFinancialAssets</t>
+          <t>ifrs-full:CurrentFinancialLiabilities</t>
         </is>
       </c>
       <c r="D6" s="38" t="n">
-        <v>1576000</v>
+        <v>4918000</v>
       </c>
       <c r="E6" s="38" t="n">
-        <v>1060000</v>
+        <v>4264000</v>
       </c>
       <c r="F6" s="38" t="n">
-        <v>295000</v>
-      </c>
-      <c r="G6" s="38" t="n">
-        <v>335000</v>
-      </c>
-      <c r="H6" s="38" t="n">
-        <v>233000</v>
-      </c>
+        <v>2622000</v>
+      </c>
+      <c r="G6" s="38" t="n"/>
+      <c r="H6" s="38" t="n"/>
       <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7093,22 +7089,28 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentDerivativeFinancialLiabilities</t>
+          <t>ifrs-full:DividendsReceivedClassifiedAsOperatingActivities</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentDerivativeFinancialLiabilities</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
+          <t>ifrs-full:DividendsReceivedClassifiedAsOperatingActivities</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="35" t="n">
+        <v>1000</v>
+      </c>
       <c r="G7" s="35" t="n">
-        <v>3622000</v>
+        <v>2000</v>
       </c>
       <c r="H7" s="35" t="n">
-        <v>3451000</v>
+        <v>0</v>
       </c>
       <c r="I7" s="36" t="inlineStr">
         <is>
@@ -7124,25 +7126,29 @@
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentFinancialLiabilities</t>
+          <t>ifrs-full:DividendsReceivedFromInvestmentsAccountedForUsingEquityMethodClassifiedAsInvestingActivities</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:CurrentFinancialLiabilities</t>
+          <t>ifrs-full:DividendsReceivedFromInvestmentsAccountedForUsingEquityMethodClassifiedAsInvestingActivities</t>
         </is>
       </c>
       <c r="D8" s="38" t="n">
-        <v>4918000</v>
+        <v>102000</v>
       </c>
       <c r="E8" s="38" t="n">
-        <v>4264000</v>
+        <v>48000</v>
       </c>
       <c r="F8" s="38" t="n">
-        <v>2622000</v>
-      </c>
-      <c r="G8" s="38" t="n"/>
-      <c r="H8" s="38" t="n"/>
+        <v>75000</v>
+      </c>
+      <c r="G8" s="38" t="n">
+        <v>177000</v>
+      </c>
+      <c r="H8" s="38" t="n">
+        <v>115000</v>
+      </c>
       <c r="I8" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7157,29 +7163,25 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:DividendsReceivedClassifiedAsOperatingActivities</t>
+          <t>ifrs-full:IncreaseDecreaseThroughAppropriationOfRetainedEarnings</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:DividendsReceivedClassifiedAsOperatingActivities</t>
+          <t>ifrs-full:IncreaseDecreaseThroughAppropriationOfRetainedEarnings</t>
         </is>
       </c>
       <c r="D9" s="35" t="n">
-        <v>3000</v>
+        <v>127000</v>
       </c>
       <c r="E9" s="35" t="n">
-        <v>0</v>
+        <v>159000</v>
       </c>
       <c r="F9" s="35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G9" s="35" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H9" s="35" t="n">
-        <v>0</v>
-      </c>
+        <v>148000</v>
+      </c>
+      <c r="G9" s="35" t="n"/>
+      <c r="H9" s="35" t="n"/>
       <c r="I9" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7194,29 +7196,25 @@
       </c>
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:DividendsReceivedFromInvestmentsAccountedForUsingEquityMethodClassifiedAsInvestingActivities</t>
+          <t>ifrs-full:NoncurrentFinancialLiabilities</t>
         </is>
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:DividendsReceivedFromInvestmentsAccountedForUsingEquityMethodClassifiedAsInvestingActivities</t>
+          <t>ifrs-full:NoncurrentFinancialLiabilities</t>
         </is>
       </c>
       <c r="D10" s="38" t="n">
-        <v>102000</v>
+        <v>2265000</v>
       </c>
       <c r="E10" s="38" t="n">
-        <v>48000</v>
+        <v>2266000</v>
       </c>
       <c r="F10" s="38" t="n">
-        <v>75000</v>
-      </c>
-      <c r="G10" s="38" t="n">
-        <v>177000</v>
-      </c>
-      <c r="H10" s="38" t="n">
-        <v>115000</v>
-      </c>
+        <v>5083000</v>
+      </c>
+      <c r="G10" s="38" t="n"/>
+      <c r="H10" s="38" t="n"/>
       <c r="I10" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7231,25 +7229,29 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:IncreaseDecreaseThroughAppropriationOfRetainedEarnings</t>
+          <t>ifrs-full:NoncurrentReceivablesDueFromRelatedParties</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:IncreaseDecreaseThroughAppropriationOfRetainedEarnings</t>
+          <t>ifrs-full:NoncurrentReceivablesDueFromRelatedParties</t>
         </is>
       </c>
       <c r="D11" s="35" t="n">
-        <v>127000</v>
+        <v>123000</v>
       </c>
       <c r="E11" s="35" t="n">
-        <v>159000</v>
+        <v>88000</v>
       </c>
       <c r="F11" s="35" t="n">
-        <v>148000</v>
-      </c>
-      <c r="G11" s="35" t="n"/>
-      <c r="H11" s="35" t="n"/>
+        <v>76000</v>
+      </c>
+      <c r="G11" s="35" t="n">
+        <v>60000</v>
+      </c>
+      <c r="H11" s="35" t="n">
+        <v>9000</v>
+      </c>
       <c r="I11" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7264,28 +7266,22 @@
       </c>
       <c r="B12" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentDerivativeFinancialAssets</t>
+          <t>ifrs-full:OtherDifferencesToCashAndCashEquivalentsInStatementOfCashFlows</t>
         </is>
       </c>
       <c r="C12" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentDerivativeFinancialAssets</t>
-        </is>
-      </c>
-      <c r="D12" s="38" t="n">
-        <v>14000</v>
-      </c>
-      <c r="E12" s="38" t="n">
-        <v>39000</v>
-      </c>
-      <c r="F12" s="38" t="n">
-        <v>1000</v>
-      </c>
+          <t>ifrs-full:OtherDifferencesToCashAndCashEquivalentsInStatementOfCashFlows</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="n"/>
+      <c r="E12" s="38" t="n"/>
+      <c r="F12" s="38" t="n"/>
       <c r="G12" s="38" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H12" s="38" t="n">
-        <v>2000</v>
+        <v>44000</v>
       </c>
       <c r="I12" s="39" t="inlineStr">
         <is>
@@ -7301,23 +7297,21 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentDerivativeFinancialLiabilities</t>
+          <t>ifrs-full:PaymentsFromChangesInOwnershipInterestsInSubsidiaries</t>
         </is>
       </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentDerivativeFinancialLiabilities</t>
-        </is>
-      </c>
-      <c r="D13" s="35" t="n"/>
+          <t>ifrs-full:PaymentsFromChangesInOwnershipInterestsInSubsidiaries</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="n">
+        <v>-11000</v>
+      </c>
       <c r="E13" s="35" t="n"/>
       <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n">
-        <v>4875000</v>
-      </c>
-      <c r="H13" s="35" t="n">
-        <v>4625000</v>
-      </c>
+      <c r="G13" s="35" t="n"/>
+      <c r="H13" s="35" t="n"/>
       <c r="I13" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7332,25 +7326,23 @@
       </c>
       <c r="B14" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentFinancialLiabilities</t>
+          <t>ifrs-full:RevenueFromSaleOfAgriculturalProduce</t>
         </is>
       </c>
       <c r="C14" s="37" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentFinancialLiabilities</t>
-        </is>
-      </c>
-      <c r="D14" s="38" t="n">
-        <v>2265000</v>
-      </c>
-      <c r="E14" s="38" t="n">
-        <v>2266000</v>
-      </c>
-      <c r="F14" s="38" t="n">
-        <v>5083000</v>
-      </c>
-      <c r="G14" s="38" t="n"/>
-      <c r="H14" s="38" t="n"/>
+          <t>ifrs-full:RevenueFromSaleOfAgriculturalProduce</t>
+        </is>
+      </c>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="38" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="38" t="n">
+        <v>60678000</v>
+      </c>
+      <c r="H14" s="38" t="n">
+        <v>61841000</v>
+      </c>
       <c r="I14" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7365,323 +7357,30 @@
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentReceivablesDueFromRelatedParties</t>
+          <t>ifrs-full:TradeAndOtherCurrentReceivablesDueFromRelatedParties</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>ifrs-full:NoncurrentReceivablesDueFromRelatedParties</t>
+          <t>ifrs-full:TradeAndOtherCurrentReceivablesDueFromRelatedParties</t>
         </is>
       </c>
       <c r="D15" s="35" t="n">
-        <v>123000</v>
+        <v>206000</v>
       </c>
       <c r="E15" s="35" t="n">
-        <v>88000</v>
+        <v>221000</v>
       </c>
       <c r="F15" s="35" t="n">
-        <v>76000</v>
+        <v>243000</v>
       </c>
       <c r="G15" s="35" t="n">
-        <v>60000</v>
+        <v>253000</v>
       </c>
       <c r="H15" s="35" t="n">
-        <v>9000</v>
+        <v>204000</v>
       </c>
       <c r="I15" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:OtherCashPaymentsToAcquireEquityOrDebtInstrumentsOfOtherEntitiesClassifiedAsInvestingActivities</t>
-        </is>
-      </c>
-      <c r="C16" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:OtherCashPaymentsToAcquireEquityOrDebtInstrumentsOfOtherEntitiesClassifiedAsInvestingActivities</t>
-        </is>
-      </c>
-      <c r="D16" s="38" t="n"/>
-      <c r="E16" s="38" t="n"/>
-      <c r="F16" s="38" t="n"/>
-      <c r="G16" s="38" t="n">
-        <v>124000</v>
-      </c>
-      <c r="H16" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B17" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:OtherComprehensiveIncomeBeforeTaxAvailableforsaleFinancialAssets</t>
-        </is>
-      </c>
-      <c r="C17" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:OtherComprehensiveIncomeBeforeTaxAvailableforsaleFinancialAssets</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="F17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="35" t="n"/>
-      <c r="H17" s="35" t="n"/>
-      <c r="I17" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:OtherDifferencesToCashAndCashEquivalentsInStatementOfCashFlows</t>
-        </is>
-      </c>
-      <c r="C18" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:OtherDifferencesToCashAndCashEquivalentsInStatementOfCashFlows</t>
-        </is>
-      </c>
-      <c r="D18" s="38" t="n"/>
-      <c r="E18" s="38" t="n"/>
-      <c r="F18" s="38" t="n"/>
-      <c r="G18" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="38" t="n">
-        <v>44000</v>
-      </c>
-      <c r="I18" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B19" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:PaymentsFromChangesInOwnershipInterestsInSubsidiaries</t>
-        </is>
-      </c>
-      <c r="C19" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:PaymentsFromChangesInOwnershipInterestsInSubsidiaries</t>
-        </is>
-      </c>
-      <c r="D19" s="35" t="n">
-        <v>-11000</v>
-      </c>
-      <c r="E19" s="35" t="n"/>
-      <c r="F19" s="35" t="n"/>
-      <c r="G19" s="35" t="n"/>
-      <c r="H19" s="35" t="n"/>
-      <c r="I19" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B20" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:ProceedsFromSalesOfInvestmentsAccountedForUsingEquityMethod</t>
-        </is>
-      </c>
-      <c r="C20" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:ProceedsFromSalesOfInvestmentsAccountedForUsingEquityMethod</t>
-        </is>
-      </c>
-      <c r="D20" s="38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E20" s="38" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F20" s="38" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G20" s="38" t="n"/>
-      <c r="H20" s="38" t="n"/>
-      <c r="I20" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B21" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:PurchaseOfInterestsInInvestmentsAccountedForUsingEquityMethod</t>
-        </is>
-      </c>
-      <c r="C21" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:PurchaseOfInterestsInInvestmentsAccountedForUsingEquityMethod</t>
-        </is>
-      </c>
-      <c r="D21" s="35" t="n">
-        <v>84000</v>
-      </c>
-      <c r="E21" s="35" t="n">
-        <v>68000</v>
-      </c>
-      <c r="F21" s="35" t="n">
-        <v>42000</v>
-      </c>
-      <c r="G21" s="35" t="n">
-        <v>80000</v>
-      </c>
-      <c r="H21" s="35" t="n">
-        <v>91000</v>
-      </c>
-      <c r="I21" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B22" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:RevenueFromSaleOfAgriculturalProduce</t>
-        </is>
-      </c>
-      <c r="C22" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:RevenueFromSaleOfAgriculturalProduce</t>
-        </is>
-      </c>
-      <c r="D22" s="38" t="n"/>
-      <c r="E22" s="38" t="n"/>
-      <c r="F22" s="38" t="n"/>
-      <c r="G22" s="38" t="n">
-        <v>60678000</v>
-      </c>
-      <c r="H22" s="38" t="n">
-        <v>61841000</v>
-      </c>
-      <c r="I22" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B23" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:ShareOfOtherComprehensiveIncomeOfAssociatesAndJointVenturesAccountedForUsingEquityMethodThatWillBeReclassifiedToProfitOrLossBeforeTax</t>
-        </is>
-      </c>
-      <c r="C23" s="34" t="inlineStr">
-        <is>
-          <t>ifrs-full:ShareOfOtherComprehensiveIncomeOfAssociatesAndJointVenturesAccountedForUsingEquityMethodThatWillBeReclassifiedToProfitOrLossBeforeTax</t>
-        </is>
-      </c>
-      <c r="D23" s="35" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="E23" s="35" t="n">
-        <v>-4000</v>
-      </c>
-      <c r="F23" s="35" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G23" s="35" t="n"/>
-      <c r="H23" s="35" t="n"/>
-      <c r="I23" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B24" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:TradeAndOtherCurrentReceivablesDueFromRelatedParties</t>
-        </is>
-      </c>
-      <c r="C24" s="37" t="inlineStr">
-        <is>
-          <t>ifrs-full:TradeAndOtherCurrentReceivablesDueFromRelatedParties</t>
-        </is>
-      </c>
-      <c r="D24" s="38" t="n">
-        <v>206000</v>
-      </c>
-      <c r="E24" s="38" t="n">
-        <v>221000</v>
-      </c>
-      <c r="F24" s="38" t="n">
-        <v>243000</v>
-      </c>
-      <c r="G24" s="38" t="n">
-        <v>253000</v>
-      </c>
-      <c r="H24" s="38" t="n">
-        <v>204000</v>
-      </c>
-      <c r="I24" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/24246930_dlg.xlsx
+++ b/filer/24246930_dlg.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (valuta pr. år - se kolonneoverskrifter)</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Resultatopgørelse t.kr.</t>
+          <t>Resultatopgørelse valuta pr. år - se kolonneoverskrifter</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -1431,7 +1431,7 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>AKTIVER t.kr.</t>
+          <t>AKTIVER valuta pr. år - se kolonneoverskrifter</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -2525,7 +2525,7 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>PASSIVER t.kr.</t>
+          <t>PASSIVER valuta pr. år - se kolonneoverskrifter</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
@@ -4366,7 +4366,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Resultatopgørelse &amp; nøgleoplysninger (t.kr.)</t>
+          <t>Resultatopgørelse &amp; nøgleoplysninger (valuta pr. år - se kolonneoverskrifter)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -4748,7 +4748,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Balance (t.kr.)</t>
+          <t>Balance (valuta pr. år - se kolonneoverskrifter)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -6728,15 +6728,15 @@
         </is>
       </c>
       <c r="B60" s="29">
-        <f>IF('balance_raw'!$F$23="","—",IF(ABS(B20-'balance_raw'!$F$23)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-'balance_raw'!$F$23,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$F$23="","—",IF(ABS(B20-'balance_raw'!$F$23)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-'balance_raw'!$F$23,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="C60" s="29">
-        <f>IF('balance_raw'!$E$23="","—",IF(ABS(C20-'balance_raw'!$E$23)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-'balance_raw'!$E$23,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$E$23="","—",IF(ABS(C20-'balance_raw'!$E$23)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-'balance_raw'!$E$23,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="D60" s="29">
-        <f>IF('balance_raw'!$D$23="","—",IF(ABS(D20-'balance_raw'!$D$23)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-'balance_raw'!$D$23,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$D$23="","—",IF(ABS(D20-'balance_raw'!$D$23)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-'balance_raw'!$D$23,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="F60" s="25" t="inlineStr">
@@ -6752,15 +6752,15 @@
         </is>
       </c>
       <c r="B61" s="29">
-        <f>IF('balance_raw'!$F$51="","—",IF(ABS(B24-'balance_raw'!$F$51)&lt;=1,"✓ OK","❌ "&amp;TEXT(B24-'balance_raw'!$F$51,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$F$51="","—",IF(ABS(B24-'balance_raw'!$F$51)&lt;=1,"✓ OK","❌ "&amp;TEXT(B24-'balance_raw'!$F$51,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="C61" s="29">
-        <f>IF('balance_raw'!$E$51="","—",IF(ABS(C24-'balance_raw'!$E$51)&lt;=1,"✓ OK","❌ "&amp;TEXT(C24-'balance_raw'!$E$51,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$E$51="","—",IF(ABS(C24-'balance_raw'!$E$51)&lt;=1,"✓ OK","❌ "&amp;TEXT(C24-'balance_raw'!$E$51,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF('balance_raw'!$D$51="","—",IF(ABS(D24-'balance_raw'!$D$51)&lt;=1,"✓ OK","❌ "&amp;TEXT(D24-'balance_raw'!$D$51,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw'!$D$51="","—",IF(ABS(D24-'balance_raw'!$D$51)&lt;=1,"✓ OK","❌ "&amp;TEXT(D24-'balance_raw'!$D$51,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="F61" s="25" t="inlineStr">
@@ -6776,15 +6776,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF(ABS(B20-B24)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-B24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(B20-B24)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-B24,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter")</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF(ABS(C20-C24)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-C24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(C20-C24)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-C24,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter")</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF(ABS(D20-D24)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-D24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(D20-D24)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-D24,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter")</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
@@ -6800,15 +6800,15 @@
         </is>
       </c>
       <c r="B63" s="29">
-        <f>IF('res_raw'!$F$4="","—",IF(ABS(B7-'res_raw'!$F$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(B7-'res_raw'!$F$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$F$4="","—",IF(ABS(B7-'res_raw'!$F$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(B7-'res_raw'!$F$4,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="C63" s="29">
-        <f>IF('res_raw'!$E$4="","—",IF(ABS(C7-'res_raw'!$E$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(C7-'res_raw'!$E$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$E$4="","—",IF(ABS(C7-'res_raw'!$E$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(C7-'res_raw'!$E$4,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="D63" s="29">
-        <f>IF('res_raw'!$D$4="","—",IF(ABS(D7-'res_raw'!$D$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(D7-'res_raw'!$D$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$D$4="","—",IF(ABS(D7-'res_raw'!$D$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(D7-'res_raw'!$D$4,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="F63" s="25" t="inlineStr">
@@ -6824,15 +6824,15 @@
         </is>
       </c>
       <c r="B64" s="29">
-        <f>IF('res_raw'!$F$9="","—",IF(ABS(B12-'res_raw'!$F$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(B12-'res_raw'!$F$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$F$9="","—",IF(ABS(B12-'res_raw'!$F$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(B12-'res_raw'!$F$9,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="C64" s="29">
-        <f>IF('res_raw'!$E$9="","—",IF(ABS(C12-'res_raw'!$E$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(C12-'res_raw'!$E$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$E$9="","—",IF(ABS(C12-'res_raw'!$E$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(C12-'res_raw'!$E$9,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="D64" s="29">
-        <f>IF('res_raw'!$D$9="","—",IF(ABS(D12-'res_raw'!$D$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(D12-'res_raw'!$D$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$D$9="","—",IF(ABS(D12-'res_raw'!$D$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(D12-'res_raw'!$D$9,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="F64" s="25" t="inlineStr">
@@ -6848,15 +6848,15 @@
         </is>
       </c>
       <c r="B65" s="29">
-        <f>IF('res_raw'!$F$14="","—",IF(ABS(B15-'res_raw'!$F$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(B15-'res_raw'!$F$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$F$14="","—",IF(ABS(B15-'res_raw'!$F$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(B15-'res_raw'!$F$14,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="C65" s="29">
-        <f>IF('res_raw'!$E$14="","—",IF(ABS(C15-'res_raw'!$E$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(C15-'res_raw'!$E$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$E$14="","—",IF(ABS(C15-'res_raw'!$E$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(C15-'res_raw'!$E$14,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="D65" s="29">
-        <f>IF('res_raw'!$D$14="","—",IF(ABS(D15-'res_raw'!$D$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(D15-'res_raw'!$D$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw'!$D$14="","—",IF(ABS(D15-'res_raw'!$D$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(D15-'res_raw'!$D$14,"+#,##0;-#,##0")&amp;" valuta pr. år - se kolonneoverskrifter"))</f>
         <v/>
       </c>
       <c r="F65" s="25" t="inlineStr">

--- a/filer/24246930_dlg.xlsx
+++ b/filer/24246930_dlg.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_funktion" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4338,6 +4339,148 @@
       </c>
       <c r="F89" s="13">
         <f>IFERROR($F$29/($F$51+$F$58)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE valuta pr. år - se kolonneoverskrifter</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B92" s="17">
+        <f>'pengestrom_raw'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C92" s="17">
+        <f>'pengestrom_raw'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D92" s="17">
+        <f>'pengestrom_raw'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E92" s="17">
+        <f>'pengestrom_raw'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F92" s="17">
+        <f>'pengestrom_raw'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B93" s="17">
+        <f>'pengestrom_raw'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C93" s="17">
+        <f>'pengestrom_raw'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D93" s="17">
+        <f>'pengestrom_raw'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E93" s="17">
+        <f>'pengestrom_raw'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F93" s="17">
+        <f>'pengestrom_raw'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B94" s="17">
+        <f>'pengestrom_raw'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C94" s="17">
+        <f>'pengestrom_raw'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D94" s="17">
+        <f>'pengestrom_raw'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E94" s="17">
+        <f>'pengestrom_raw'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F94" s="17">
+        <f>'pengestrom_raw'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B95" s="17">
+        <f>'pengestrom_raw'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C95" s="17">
+        <f>'pengestrom_raw'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D95" s="17">
+        <f>'pengestrom_raw'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E95" s="17">
+        <f>'pengestrom_raw'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F95" s="17">
+        <f>'pengestrom_raw'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B96">
+        <f>IF(ABS(('pengestrom_raw'!$B$2+'pengestrom_raw'!$B$3+'pengestrom_raw'!$B$4)-'pengestrom_raw'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$B$2+'pengestrom_raw'!$B$3+'pengestrom_raw'!$B$4)-'pengestrom_raw'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C96">
+        <f>IF(ABS(('pengestrom_raw'!$C$2+'pengestrom_raw'!$C$3+'pengestrom_raw'!$C$4)-'pengestrom_raw'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$C$2+'pengestrom_raw'!$C$3+'pengestrom_raw'!$C$4)-'pengestrom_raw'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D96">
+        <f>IF(ABS(('pengestrom_raw'!$D$2+'pengestrom_raw'!$D$3+'pengestrom_raw'!$D$4)-'pengestrom_raw'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$D$2+'pengestrom_raw'!$D$3+'pengestrom_raw'!$D$4)-'pengestrom_raw'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E96">
+        <f>IF(ABS(('pengestrom_raw'!$E$2+'pengestrom_raw'!$E$3+'pengestrom_raw'!$E$4)-'pengestrom_raw'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$E$2+'pengestrom_raw'!$E$3+'pengestrom_raw'!$E$4)-'pengestrom_raw'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F96">
+        <f>IF(ABS(('pengestrom_raw'!$F$2+'pengestrom_raw'!$F$3+'pengestrom_raw'!$F$4)-'pengestrom_raw'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw'!$F$2+'pengestrom_raw'!$F$3+'pengestrom_raw'!$F$4)-'pengestrom_raw'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4386,342 +4529,342 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>54551000</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>74875000</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>62443000</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>56081000</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>57123000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Produktionsomkostninger</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>49051000</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>68421000</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>56139000</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>50273000</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>51347000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>5500000</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>6454000</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>6304000</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>5808000</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>5776000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Salgs- og distributionsomkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>3563000</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>3939000</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>3754000</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>3861000</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>3895000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Administrationsomkostninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>1019000</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>1234000</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>1349000</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>1353000</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>1457000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>210000</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>270000</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>188000</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>386000</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>302000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>33000</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>55000</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>33000</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>18000</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>22000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>1194000</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>1612000</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>1602000</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>846000</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>445000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n">
         <v>181000</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>262000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>14000</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>21000</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>44000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>32000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>22000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>306000</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>329000</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>627000</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>931000</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>659000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>902000</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>1304000</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>1019000</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>-53000</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>-192000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>169000</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>230000</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>259000</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>132000</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>160000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>733000</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>1074000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>760000</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>-185000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>-352000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4768,904 +4911,904 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="16" t="n"/>
-      <c r="D2" s="16" t="n"/>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n">
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n">
         <v>2998000</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>3046000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>3381000</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>3485000</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>3572000</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>652000</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>503000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>9059000</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>8747000</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>8990000</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>8704000</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>8495000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>2238000</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>2484000</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>2687000</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>2628000</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>2913000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>239000</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>342000</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>729000</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>650000</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>573000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>15321000</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>15629000</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>16538000</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>16106000</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>15915000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>5578000</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>5996000</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>5623000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>5792000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>5679000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>2724000</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>3144000</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>2576000</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>2562000</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>2176000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>3677000</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>3436000</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>2506000</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>666000</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>634000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n">
         <v>358000</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>197000</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>193000</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>165000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>238000</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>419000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>427000</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>369000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>354000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>43000</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>63000</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>113000</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>114000</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>207000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>800000</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>876000</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>732000</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>752000</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <v>581000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>404000</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>382000</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>280000</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>307000</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="17" t="n">
         <v>474000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>11741000</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>12100000</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>10059000</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <v>10308000</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="17" t="n">
         <v>9719000</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>27062000</v>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>27729000</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>26597000</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>26414000</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="17" t="n">
         <v>25634000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>1353000</v>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>1472000</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>1590000</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>1663000</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="17" t="n">
         <v>1607000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B28" s="17" t="n">
         <v>2311000</v>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="17" t="n">
         <v>1039000</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <v>1155000</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <v>1300000</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="17" t="n">
         <v>1123000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>698000</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>2714000</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>2916000</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>2563000</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="17" t="n">
         <v>2129000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
+      <c r="B30" s="17" t="n">
         <v>7339000</v>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>8248000</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>8575000</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>8206000</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F30" s="17" t="n">
         <v>7560000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
+      <c r="B31" s="17" t="n">
         <v>472000</v>
       </c>
-      <c r="C31" s="16" t="n">
+      <c r="C31" s="17" t="n">
         <v>485000</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>503000</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>453000</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="F31" s="17" t="n">
         <v>460000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>210000</v>
       </c>
-      <c r="C32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>156000</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>141000</v>
       </c>
-      <c r="E32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>140000</v>
       </c>
-      <c r="F32" s="16" t="n">
+      <c r="F32" s="17" t="n">
         <v>132000</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
+      <c r="B35" s="17" t="n">
         <v>1456000</v>
       </c>
-      <c r="C35" s="16" t="n">
+      <c r="C35" s="17" t="n">
         <v>1410000</v>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="D35" s="17" t="n">
         <v>1257000</v>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="E35" s="17" t="n">
         <v>1137000</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="F35" s="17" t="n">
         <v>1068000</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>271000</v>
       </c>
-      <c r="C36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>233000</v>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>198000</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>5070000</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="F36" s="17" t="n">
         <v>4821000</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>4748000</v>
       </c>
-      <c r="C37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>4621000</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>7265000</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>6862000</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="F37" s="17" t="n">
         <v>6571000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n">
+      <c r="B41" s="17" t="n">
         <v>195000</v>
       </c>
-      <c r="C41" s="16" t="n">
+      <c r="C41" s="17" t="n">
         <v>208000</v>
       </c>
-      <c r="D41" s="16" t="n">
+      <c r="D41" s="17" t="n">
         <v>212000</v>
       </c>
-      <c r="E41" s="16" t="n">
+      <c r="E41" s="17" t="n">
         <v>191000</v>
       </c>
-      <c r="F41" s="16" t="n">
+      <c r="F41" s="17" t="n">
         <v>172000</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
+      <c r="B42" s="17" t="n">
         <v>3990000</v>
       </c>
-      <c r="C42" s="16" t="n">
+      <c r="C42" s="17" t="n">
         <v>4245000</v>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="D42" s="17" t="n">
         <v>2973000</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="E42" s="17" t="n">
         <v>2871000</v>
       </c>
-      <c r="F42" s="16" t="n">
+      <c r="F42" s="17" t="n">
         <v>3502000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
+      <c r="B47" s="17" t="n">
         <v>1765000</v>
       </c>
-      <c r="C47" s="16" t="n">
+      <c r="C47" s="17" t="n">
         <v>2114000</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <v>1883000</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E47" s="17" t="n">
         <v>5397000</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="F47" s="17" t="n">
         <v>5280000</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n">
+      <c r="B49" s="17" t="n">
         <v>14975000</v>
       </c>
-      <c r="C49" s="16" t="n">
+      <c r="C49" s="17" t="n">
         <v>14860000</v>
       </c>
-      <c r="D49" s="16" t="n">
+      <c r="D49" s="17" t="n">
         <v>10757000</v>
       </c>
-      <c r="E49" s="16" t="n">
+      <c r="E49" s="17" t="n">
         <v>11346000</v>
       </c>
-      <c r="F49" s="16" t="n">
+      <c r="F49" s="17" t="n">
         <v>11503000</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n">
+      <c r="B50" s="17" t="n">
         <v>19723000</v>
       </c>
-      <c r="C50" s="16" t="n">
+      <c r="C50" s="17" t="n">
         <v>19481000</v>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="D50" s="17" t="n">
         <v>18022000</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="E50" s="17" t="n">
         <v>18208000</v>
       </c>
-      <c r="F50" s="16" t="n">
+      <c r="F50" s="17" t="n">
         <v>18074000</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n">
+      <c r="B51" s="17" t="n">
         <v>27062000</v>
       </c>
-      <c r="C51" s="16" t="n">
+      <c r="C51" s="17" t="n">
         <v>27729000</v>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="D51" s="17" t="n">
         <v>26597000</v>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="E51" s="17" t="n">
         <v>26414000</v>
       </c>
-      <c r="F51" s="16" t="n">
+      <c r="F51" s="17" t="n">
         <v>25634000</v>
       </c>
     </row>
@@ -5675,6 +5818,138 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (valuta pr. år - se kolonneoverskrifter)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>635000</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>1024000</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>343000</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>575000</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>1592000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-1148000</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-790000</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-1530000</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-706000</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-592000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>736000</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-256000</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>1085000</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>158000</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-789000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>208000</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>-22000</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>-102000</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>211000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6873,7 +7148,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
